--- a/outputs/evaluation/decision/v2/CF_M01/run_1/CF_M01_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M01/run_1/CF_M01_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,49 +471,145 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M01_AD01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Security; Scalability; Availability and reliability</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Service-oriented</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>The objective of these services is to form a data lake where all history is stored so that it can be processed in the analytical module. The system must be able to grow in capacity when the data volume increases. The system scales automatically as data increases.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7383999999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>CF_M01_AD03</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Gives the ability to handle partial system crashes</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>*CF_M01_C08</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>43</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Resilience</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>AD_02</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>The objective of these services is to form a data lake where all history is stored so that it can be processed in the analytical module, improving the scalability and availability of the system.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6073</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>The objective of these services is to form a data lake where all history is stored so that it can be processed in the analytical module. The system must be able to grow in capacity when the data volume increases. The system scales automatically as data increases.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5786</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>*CF_M01_C09, *CF_M01_C10</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Price; Experience</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AWS cloud services set</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>AWS is used for infrastructure. It is the set of cloud computing services that allows the creation of scalable and highly available applications.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6587</v>
       </c>
     </row>
   </sheetData>
